--- a/Result/profitability/2704.xlsx
+++ b/Result/profitability/2704.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07125000000000004</v>
+        <v>0.23125</v>
       </c>
       <c r="N2" t="n">
-        <v>33.4425</v>
+        <v>33.8175</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>1</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.35</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08624999999999997</v>
+        <v>0.35</v>
       </c>
       <c r="N3" t="n">
-        <v>38.83</v>
+        <v>39.275</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,13 +899,13 @@
         <v>0.26</v>
       </c>
       <c r="M4" t="n">
-        <v>0.19375</v>
+        <v>0.5137499999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>43.87875</v>
+        <v>43.49125</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.02</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3275</v>
+        <v>0.43625</v>
       </c>
       <c r="N5" t="n">
-        <v>36.00375</v>
+        <v>36.07875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.02</v>
       </c>
       <c r="M6" t="n">
-        <v>0.25</v>
+        <v>0.265</v>
       </c>
       <c r="N6" t="n">
-        <v>37.22625</v>
+        <v>38.2725</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.08874999999999998</v>
+        <v>0.3275</v>
       </c>
       <c r="N7" t="n">
-        <v>39.15375</v>
+        <v>39.22625000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="n">
         <v>98.2</v>
@@ -1391,13 +1391,13 @@
         <v>0.24</v>
       </c>
       <c r="M8" t="n">
-        <v>0.16875</v>
+        <v>0.3375</v>
       </c>
       <c r="N8" t="n">
-        <v>40.56375</v>
+        <v>40.61375</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2704</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>327</v>
+      </c>
+      <c r="D75" t="n">
+        <v>228</v>
+      </c>
+      <c r="E75" t="n">
+        <v>99</v>
+      </c>
+      <c r="F75" t="n">
+        <v>30.29</v>
+      </c>
+      <c r="G75" t="n">
+        <v>10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.97%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>712</v>
+      </c>
+      <c r="J75" t="n">
+        <v>721</v>
+      </c>
+      <c r="K75" t="n">
+        <v>553</v>
+      </c>
+      <c r="L75" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.09249999999999997</v>
+      </c>
+      <c r="N75" t="n">
+        <v>28.61375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X75" t="n">
+        <v>8.4375</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0.3999999999999986</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.01338240214118436</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.87</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>1.359375</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0.5999999999999979</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.02020882452004025</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
